--- a/content/Consulting/05_Tobe전략/노드_아이디어_매핑_260427.xlsx
+++ b/content/Consulting/05_Tobe전략/노드_아이디어_매핑_260427.xlsx
@@ -593,13 +593,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="75" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -752,7 +752,7 @@
               <color rgb="003F4F8B"/>
               <sz val="11"/>
             </rPr>
-            <t>F-2</t>
+            <t>F-6</t>
           </r>
         </is>
       </c>
@@ -1111,6 +1111,23 @@
               <color rgb="002F5496"/>
               <sz val="11"/>
             </rPr>
+            <t>A-3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
             <t>A-5</t>
           </r>
           <r>
@@ -1128,7 +1145,7 @@
               <color rgb="003F4F8B"/>
               <sz val="11"/>
             </rPr>
-            <t>F-6</t>
+            <t>F-14</t>
           </r>
         </is>
       </c>
@@ -2131,6 +2148,53 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
+            <t>첫 투자상품 매수 완료 넛지 → 부모</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀의 첫 매수 시점 알림</t>
+          </r>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-5</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="50" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>S1  금융 감각 형성기 (7~9세)</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>📣 넛지</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="10"/>
+            </rPr>
             <t>S2 진입 필요 넛지 → 부모</t>
           </r>
           <r>
@@ -2144,46 +2208,7 @@
           </r>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="50" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>S2  선택 체험기 (10~12세)</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>이벤트</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="10"/>
-            </rPr>
-            <t>자녀 연령 10세 도달 / 소비 품목 다양화</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비 카테고리 증가 체감 인식 후 진입</t>
-          </r>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2197,7 +2222,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>이벤트</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -2209,16 +2234,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>또래 소비 문화 진입</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-또래와 함께 편의점/노래방 등을 처음 함께 소비</t>
+            <t>자녀 연령 10세 도달 / 소비 품목 다양화</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비 카테고리 증가 체감 인식 후 진입</t>
           </r>
         </is>
       </c>
@@ -2248,30 +2273,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>소비 실패 경험</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-용돈을 다 써버리고 남은 날들을 버텨봄 → 계획 없이 쓰면 어떻게 되는지 처음 인식</t>
-          </r>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-1</t>
-          </r>
+            <t>또래 소비 문화 진입</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+또래와 함께 편의점/노래방 등을 처음 함께 소비</t>
+          </r>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2300,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -2295,16 +2312,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>소비 실패 교육</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-중간에 돈을 다 쓴 자녀에게 돈을 주지 않음 → 불편함이 교육이 됨</t>
+            <t>소비 실패 경험</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+용돈을 다 써버리고 남은 날들을 버텨봄 → 계획 없이 쓰면 어떻게 되는지 처음 인식</t>
           </r>
         </is>
       </c>
@@ -2314,10 +2331,27 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00548235"/>
-              <sz val="11"/>
-            </rPr>
-            <t>C-1</t>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-10</t>
           </r>
         </is>
       </c>
@@ -2330,7 +2364,7 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -2342,22 +2376,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>직접 소비 경험 / 계획 소비 시작</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-용돈 카테고리 증가 + 계획 소비 시작 단계</t>
-          </r>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>소비 실패 교육</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+중간에 돈을 다 쓴 자녀에게 돈을 주지 않음 → 불편함이 교육이 됨</t>
+          </r>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00548235"/>
+              <sz val="11"/>
+            </rPr>
+            <t>C-1</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2369,7 +2411,7 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
@@ -2381,16 +2423,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 주기 변경 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀) 주간으로 용돈을 받아 더 큰 금액을 자유롭게 계획해서 소비하라는 안내</t>
+            <t>직접 소비 경험 / 계획 소비 시작</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+용돈 카테고리 증가 + 계획 소비 시작 단계</t>
           </r>
         </is>
       </c>
@@ -2408,7 +2450,7 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
@@ -2420,30 +2462,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>정기 용돈 설정 (매일)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-용돈 지급 필요성 안내. 추천금액 확인 후 용돈 금액 설정</t>
-          </r>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00548235"/>
-              <sz val="11"/>
-            </rPr>
-            <t>C-3</t>
-          </r>
+            <t>용돈 주기 변경 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀) 주간으로 용돈을 받아 더 큰 금액을 자유롭게 계획해서 소비하라는 안내</t>
+          </r>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2489,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -2467,22 +2501,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매일 용돈 수령 시작</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-예측 가능한 수입 생김</t>
-          </r>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>정기 용돈 설정 (매일)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+용돈 지급 필요성 안내. 추천금액 확인 후 용돈 금액 설정</t>
+          </r>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00548235"/>
+              <sz val="11"/>
+            </rPr>
+            <t>C-3</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2506,16 +2548,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>계획 소비 시작</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-쓸 돈 · 비상금 나눠 사용</t>
+            <t>매일 용돈 수령 시작</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+예측 가능한 수입 생김</t>
           </r>
         </is>
       </c>
@@ -2545,16 +2587,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 주기 변경 요청</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비 현황 확인 후 결정</t>
+            <t>계획 소비 시작</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+쓸 돈 · 비상금 나눠 사용</t>
           </r>
         </is>
       </c>
@@ -2572,7 +2614,7 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
@@ -2584,30 +2626,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 일→주 전환</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자동이체 시작 / 자금 분활 관리</t>
-          </r>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-3</t>
-          </r>
+            <t>용돈 주기 변경 요청</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비 현황 확인 후 결정</t>
+          </r>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2653,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -2631,22 +2665,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>투자 경험 유도 넛지 → 부모</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-부모) 자녀에게 투자 개념을 이해시키기 위해 종목 선택지를 제공하고, 함께 투자해 보라는 안내</t>
-          </r>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>용돈 일→주 전환</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자동이체 시작 / 자금 분활 관리</t>
+          </r>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-3</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2658,7 +2700,7 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
@@ -2670,16 +2712,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>투자 옵션 A/B 제안</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-종목 선택 카드 제시. 부모가 직접 종목 선택지를 큐레이션</t>
+            <t>투자 경험 유도 넛지 → 부모</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+부모) 자녀에게 투자 개념을 이해시키기 위해 종목 선택지를 제공하고, 함께 투자해 보라는 안내</t>
           </r>
         </is>
       </c>
@@ -2697,7 +2739,7 @@
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -2709,16 +2751,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>투자 상품 직접 선택</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-부모가 제안한 옵션 중 종목 선택 → 투자 첫 경험</t>
+            <t>투자 옵션 A/B 제안</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+종목 선택 카드 제시. 부모가 직접 종목 선택지를 큐레이션</t>
           </r>
         </is>
       </c>
@@ -2748,22 +2790,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>투자 계좌 확인 및 관심 증가</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-배당·이자 발생 구조 확인 → 투자 개념 이해</t>
-          </r>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>투자 상품 직접 선택</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+부모가 제안한 옵션 중 종목 선택 → 투자 첫 경험</t>
+          </r>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-12</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2787,16 +2837,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>이벤트 자금 투자계좌로 이체</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-세뱃돈·조부모 용돈 입금</t>
+            <t>투자 계좌 확인 및 관심 증가</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+배당·이자 발생 구조 확인 → 투자 개념 이해</t>
           </r>
         </is>
       </c>
@@ -2806,10 +2856,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-6</t>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-6</t>
           </r>
         </is>
       </c>
@@ -2834,22 +2884,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭저축 금액 투자계좌로 이체</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-매칭 저축으로 모은 돈을 투자 시드로 전환</t>
-          </r>
-        </is>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>이벤트 자금 투자계좌로 이체</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+세뱃돈·조부모 용돈 입금</t>
+          </r>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-6</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2873,16 +2931,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>ETF 소액 정기 매수 시작</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-ETF 자동 매수 습관화</t>
+            <t>매칭저축 금액 투자계좌로 이체</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+매칭 저축으로 모은 돈을 투자 시드로 전환</t>
           </r>
         </is>
       </c>
@@ -2895,7 +2953,7 @@
               <color rgb="002F5496"/>
               <sz val="11"/>
             </rPr>
-            <t>A-4</t>
+            <t>A-3</t>
           </r>
         </is>
       </c>
@@ -2908,7 +2966,7 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -2920,22 +2978,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>미션 저축 경험 넛지 → 자녀/부모</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-심부름 등을 통해 돈을 모아보는 경험 필요성 안내</t>
-          </r>
-        </is>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>ETF 소액 정기 매수 시작</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+ETF 자동 매수 습관화</t>
+          </r>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-4</t>
+          </r>
         </is>
       </c>
     </row>
@@ -2947,7 +3013,7 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -2959,47 +3025,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>미션 저축 설계</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀) 직접 미션 저축을 설계해서 돈을 모아 원하는 걸 살 수 있다는 안내</t>
-          </r>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-4</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ·  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-5</t>
-          </r>
+            <t>미션 저축 경험 넛지 → 자녀/부모</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+심부름 등을 통해 돈을 모아보는 경험 필요성 안내</t>
+          </r>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3052,7 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -3023,22 +3064,64 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>미션 저축 수락</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-희망 항목 확인 / 조건 확인 및 수락</t>
-          </r>
-        </is>
-      </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>미션 저축 설계</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀) 직접 미션 저축을 설계해서 돈을 모아 원하는 걸 살 수 있다는 안내</t>
+          </r>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00548235"/>
+              <sz val="11"/>
+            </rPr>
+            <t>C-2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-5</t>
+          </r>
         </is>
       </c>
     </row>
@@ -3050,7 +3133,7 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -3062,16 +3145,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>목표 저축 진행</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자금 분할 후 저축 자동이체</t>
+            <t>미션 저축 수락</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+희망 항목 확인 / 조건 확인 및 수락</t>
           </r>
         </is>
       </c>
@@ -3089,7 +3172,7 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -3101,16 +3184,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>미션 저축 달성 알림 수신</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-부족한 금액 자녀에게 이체 / 구매 지원</t>
+            <t>목표 저축 진행</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자금 분할 후 저축 자동이체</t>
           </r>
         </is>
       </c>
@@ -3128,7 +3211,7 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>⭐ 핵심</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -3140,16 +3223,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>미션 &amp; 공동구매</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-"내가 모은 것 + 엄마 보탠 것 = 내 것!"</t>
+            <t>미션 저축 달성 알림 수신</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+부족한 금액 자녀에게 이체 / 구매 지원</t>
           </r>
         </is>
       </c>
@@ -3159,10 +3242,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-5</t>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-5</t>
           </r>
         </is>
       </c>
@@ -3175,7 +3258,7 @@
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>⭐ 핵심</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
@@ -3187,22 +3270,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭 저축 경험 넛지 → 자녀/부모</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-미션 저축 경험 이후 매칭 저축 넛지 제공</t>
-          </r>
-        </is>
-      </c>
-      <c r="D59" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>미션 &amp; 공동구매</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+"내가 모은 것 + 엄마 보탠 것 = 내 것!"</t>
+          </r>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-5</t>
+          </r>
         </is>
       </c>
     </row>
@@ -3214,7 +3305,7 @@
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -3226,47 +3317,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭 저축 설계</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀) 비상금을 저축의 형태로 모으면 부모님이 매칭으로 지원해준다는 정기 저축 시작</t>
-          </r>
-        </is>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="11"/>
-            </rPr>
-            <t>A-1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ·  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="11"/>
-            </rPr>
-            <t>A-2</t>
-          </r>
+            <t>매칭 저축 경험 넛지 → 자녀/부모</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+미션 저축 경험 이후 매칭 저축 넛지 제공</t>
+          </r>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3344,7 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
@@ -3290,22 +3356,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭 저축 제안 수락</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-추천 비율 확인 및 매칭 저축 설계 / 조건 확인 및 수락</t>
-          </r>
-        </is>
-      </c>
-      <c r="D61" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>매칭 저축 설계</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀) 비상금을 저축의 형태로 모으면 부모님이 매칭으로 지원해준다는 정기 저축 시작</t>
+          </r>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-2</t>
+          </r>
         </is>
       </c>
     </row>
@@ -3317,7 +3391,7 @@
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -3329,16 +3403,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭 저축 진행</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자금 분할 후 저축 자동이체</t>
+            <t>매칭 저축 제안 수락</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+추천 비율 확인 및 매칭 저축 설계 / 조건 확인 및 수락</t>
           </r>
         </is>
       </c>
@@ -3352,23 +3426,6 @@
               <sz val="11"/>
             </rPr>
             <t>A-1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ·  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-7</t>
           </r>
         </is>
       </c>
@@ -3381,7 +3438,7 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C63" s="14" t="inlineStr">
@@ -3393,16 +3450,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭 저축 달성 알림 수신</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-매칭 금액 자녀에게 이체</t>
+            <t>매칭 저축 진행</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자금 분할 후 저축 자동이체</t>
           </r>
         </is>
       </c>
@@ -3412,10 +3469,27 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="009C2B2B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>E-4</t>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-7</t>
           </r>
         </is>
       </c>
@@ -3428,7 +3502,7 @@
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>⭐ 핵심</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -3440,16 +3514,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭 달성 경험</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-"아낀 만큼 엄마가 보태줬어!" 핵심 경험</t>
+            <t>매칭 저축 달성 알림 수신</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+매칭 금액 자녀에게 이체</t>
           </r>
         </is>
       </c>
@@ -3462,7 +3536,7 @@
               <color rgb="009C2B2B"/>
               <sz val="11"/>
             </rPr>
-            <t>E-1</t>
+            <t>E-4</t>
           </r>
           <r>
             <rPr>
@@ -3476,10 +3550,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="009C2B2B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>E-3</t>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-5</t>
           </r>
         </is>
       </c>
@@ -3492,7 +3566,7 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>⭐ 핵심</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
@@ -3504,16 +3578,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>월간 리포트 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀 저축·투자 패턴 성장 인식</t>
+            <t>매칭 달성 경험</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+"아낀 만큼 엄마가 보태줬어!" 핵심 경험</t>
           </r>
         </is>
       </c>
@@ -3523,10 +3597,27 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="003F4F8B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>F-1</t>
+              <color rgb="009C2B2B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>E-1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="009C2B2B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>E-3</t>
           </r>
         </is>
       </c>
@@ -3539,10 +3630,74 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
+          <t>🟢 부모</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="10"/>
+            </rPr>
+            <t>월간 리포트 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀 저축·투자 패턴 성장 인식</t>
+          </r>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-2</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="50" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>S2  선택 체험기 (10~12세)</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
           <t>📣 넛지</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3564,7 +3719,7 @@
           </r>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3574,70 +3729,6 @@
               <sz val="11"/>
             </rPr>
             <t>D-7</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="50" customHeight="1">
-      <c r="A67" s="17" t="inlineStr">
-        <is>
-          <t>S3  자율 확장기 (13~15세)</t>
-        </is>
-      </c>
-      <c r="B67" s="18" t="inlineStr">
-        <is>
-          <t>이벤트</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="10"/>
-            </rPr>
-            <t>자녀 중학교 입학</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비 품목 증가 및 직접 상품 선택 및 투자 경험</t>
-          </r>
-        </is>
-      </c>
-      <c r="D67" s="20" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-4</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ·  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="003F4F8B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>F-3</t>
           </r>
         </is>
       </c>
@@ -3650,7 +3741,7 @@
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>이벤트</t>
         </is>
       </c>
       <c r="C68" s="19" t="inlineStr">
@@ -3662,16 +3753,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>금융 대화</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀와 지속적으로 금융에 대해 대화. 답은 주지 않으며 함께 생각하는 방식</t>
+            <t>자녀 중학교 입학</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비 품목 증가 및 직접 상품 선택 및 투자 경험</t>
           </r>
         </is>
       </c>
@@ -3681,10 +3772,27 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
               <color rgb="003F4F8B"/>
               <sz val="11"/>
             </rPr>
-            <t>F-5</t>
+            <t>F-7</t>
           </r>
         </is>
       </c>
@@ -3697,7 +3805,7 @@
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
@@ -3709,16 +3817,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>또래 소비 문화 압력</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-또래와 카페·편의점 등의 지출이 늘어남. 또래의 토스·카카오뱅크 결제를 보고 자연스레 따라 사용</t>
+            <t>금융 대화</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀와 지속적으로 금융에 대해 대화. 답은 주지 않으며 함께 생각하는 방식</t>
           </r>
         </is>
       </c>
@@ -3728,44 +3836,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00548235"/>
-              <sz val="11"/>
-            </rPr>
-            <t>C-5</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ·  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
               <color rgb="003F4F8B"/>
               <sz val="11"/>
             </rPr>
-            <t>F-3</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ·  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00843C7A"/>
-              <sz val="11"/>
-            </rPr>
-            <t>G-1</t>
+            <t>F-13</t>
           </r>
         </is>
       </c>
@@ -3790,16 +3864,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>충동 소비 발생</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-예산 계획 없이 쓴 날과 계획하고 쓴 날이 공존하기 시작</t>
+            <t>또래 소비 문화 압력</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+또래와 카페·편의점 등의 지출이 늘어남. 또래의 토스·카카오뱅크 결제를 보고 자연스레 따라 사용</t>
           </r>
         </is>
       </c>
@@ -3809,10 +3883,61 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-1</t>
+              <color rgb="00548235"/>
+              <sz val="11"/>
+            </rPr>
+            <t>C-5</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-8</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-11</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00843C7A"/>
+              <sz val="11"/>
+            </rPr>
+            <t>G-1</t>
           </r>
         </is>
       </c>
@@ -3825,7 +3950,7 @@
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
@@ -3837,22 +3962,47 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 주기 변경 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀) 달별로 용돈을 받아 더 큰 금액을 자유롭게 계획해서 소비</t>
-          </r>
-        </is>
-      </c>
-      <c r="D71" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>충동 소비 발생</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+예산 계획 없이 쓴 날과 계획하고 쓴 날이 공존하기 시작</t>
+          </r>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-10</t>
+          </r>
         </is>
       </c>
     </row>
@@ -3876,16 +4026,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>S3 진입 필요 넛지 → 부모</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀가 결정하고, 부모가 승인하는 구조로 변경 필요성 안내</t>
+            <t>용돈 주기 변경 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀) 달별로 용돈을 받아 더 큰 금액을 자유롭게 계획해서 소비</t>
           </r>
         </is>
       </c>
@@ -3903,7 +4053,7 @@
       </c>
       <c r="B73" s="18" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C73" s="19" t="inlineStr">
@@ -3915,30 +4065,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>S3 - 자녀 주도 구조 동의</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-통계자료 및 내역기반 용돈 요청 → 소비 현황 확인 후 결정</t>
-          </r>
-        </is>
-      </c>
-      <c r="D73" s="20" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-6</t>
-          </r>
+            <t>S3 진입 필요 넛지 → 부모</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀가 결정하고, 부모가 승인하는 구조로 변경 필요성 안내</t>
+          </r>
+        </is>
+      </c>
+      <c r="D73" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3950,7 +4092,7 @@
       </c>
       <c r="B74" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C74" s="19" t="inlineStr">
@@ -3962,22 +4104,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>S3 진입 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-"이제 내가 먼저 제안하는구나" 인지</t>
-          </r>
-        </is>
-      </c>
-      <c r="D74" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>S3 - 자녀 주도 구조 동의</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+통계자료 및 내역기반 용돈 요청 → 소비 현황 확인 후 결정</t>
+          </r>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-6</t>
+          </r>
         </is>
       </c>
     </row>
@@ -4001,16 +4151,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 주기 변경 요청</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-통계자료 및 내역기반 용돈 요청</t>
+            <t>S3 진입 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+"이제 내가 먼저 제안하는구나" 인지</t>
           </r>
         </is>
       </c>
@@ -4028,7 +4178,7 @@
       </c>
       <c r="B76" s="18" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C76" s="19" t="inlineStr">
@@ -4040,16 +4190,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>월별 정기 용돈으로 변경</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비 현황 확인 후 결정</t>
+            <t>용돈 주기 변경 요청</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+통계자료 및 내역기반 용돈 요청</t>
           </r>
         </is>
       </c>
@@ -4067,7 +4217,7 @@
       </c>
       <c r="B77" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C77" s="19" t="inlineStr">
@@ -4079,30 +4229,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈을 소비/저축/투자로 나눠 배분</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-세 자금의 역할이 각각 다름을 인식</t>
-          </r>
-        </is>
-      </c>
-      <c r="D77" s="20" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-2</t>
-          </r>
+            <t>월별 정기 용돈으로 변경</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비 현황 확인 후 결정</t>
+          </r>
+        </is>
+      </c>
+      <c r="D77" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4126,16 +4268,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>사고 싶은 것 + 자신이 모을 금액 제안</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-"내가 OO 사려고 OO원씩 모을테니까 엄마는 나중에 OO원 지원해줘"</t>
+            <t>용돈을 소비/저축/투자로 나눠 배분</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+세 자금의 역할이 각각 다름을 인식</t>
           </r>
         </is>
       </c>
@@ -4148,7 +4290,7 @@
               <color rgb="00B89B0E"/>
               <sz val="11"/>
             </rPr>
-            <t>B-4</t>
+            <t>B-2</t>
           </r>
         </is>
       </c>
@@ -4161,7 +4303,7 @@
       </c>
       <c r="B79" s="18" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C79" s="19" t="inlineStr">
@@ -4173,22 +4315,47 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>자녀 제안 알림 수신</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-구매 희망 항목 및 자녀·부모 부담 금액 확인</t>
-          </r>
-        </is>
-      </c>
-      <c r="D79" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>사고 싶은 것 + 자신이 모을 금액 제안</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+"내가 OO 사려고 OO원씩 모을테니까 엄마는 나중에 OO원 지원해줘"</t>
+          </r>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00548235"/>
+              <sz val="11"/>
+            </rPr>
+            <t>C-2</t>
+          </r>
         </is>
       </c>
     </row>
@@ -4200,7 +4367,7 @@
       </c>
       <c r="B80" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C80" s="19" t="inlineStr">
@@ -4212,16 +4379,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>부모 수락 확인 후 미션저축 시작</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-꾸준히 모으는 루틴 형성</t>
+            <t>자녀 제안 알림 수신</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+구매 희망 항목 및 자녀·부모 부담 금액 확인</t>
           </r>
         </is>
       </c>
@@ -4251,16 +4418,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>미션 저축계좌 내 저축액이 조금씩 쌓임</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-저축액을 확인하며 성취감 느낌</t>
+            <t>부모 수락 확인 후 미션저축 시작</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+꾸준히 모으는 루틴 형성</t>
           </r>
         </is>
       </c>
@@ -4278,7 +4445,7 @@
       </c>
       <c r="B82" s="18" t="inlineStr">
         <is>
-          <t>⭐ 핵심</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C82" s="19" t="inlineStr">
@@ -4290,30 +4457,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>미션 저축 목표 달성</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-부모가 나머지를 보태 공동구매. "내가 설계한 목표 달성" 주체감 경험</t>
-          </r>
-        </is>
-      </c>
-      <c r="D82" s="20" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-5</t>
-          </r>
+            <t>미션 저축계좌 내 저축액이 조금씩 쌓임</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+저축액을 확인하며 성취감 느낌</t>
+          </r>
+        </is>
+      </c>
+      <c r="D82" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4484,7 @@
       </c>
       <c r="B83" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>⭐ 핵심</t>
         </is>
       </c>
       <c r="C83" s="19" t="inlineStr">
@@ -4337,16 +4496,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>스스로 저축 목표 금액을 정해 부모에게 제안</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-"내가 OO원 모을테니까 엄마는 0.5배 비율인 OO원씩 넣어줘"</t>
+            <t>미션 저축 목표 달성</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+부모가 나머지를 보태 공동구매. "내가 설계한 목표 달성" 주체감 경험</t>
           </r>
         </is>
       </c>
@@ -4356,10 +4515,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-1</t>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-5</t>
           </r>
         </is>
       </c>
@@ -4372,7 +4531,7 @@
       </c>
       <c r="B84" s="18" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C84" s="19" t="inlineStr">
@@ -4384,22 +4543,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>자녀 저축 목표 제안 알림 수신</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-저축 목표 금액 확인 → 매칭 비율을 조정하거나 그대로 수락</t>
-          </r>
-        </is>
-      </c>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>스스로 저축 목표 금액을 정해 부모에게 제안</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+"내가 OO원 모을테니까 엄마는 0.5배 비율인 OO원씩 넣어줘"</t>
+          </r>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-1</t>
+          </r>
         </is>
       </c>
     </row>
@@ -4411,7 +4578,7 @@
       </c>
       <c r="B85" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C85" s="19" t="inlineStr">
@@ -4423,16 +4590,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>부모 수락 확인 후 매칭저축 시작</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-꾸준히 모으는 루틴 형성</t>
+            <t>자녀 저축 목표 제안 알림 수신</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+저축 목표 금액 확인 → 매칭 비율을 조정하거나 그대로 수락</t>
           </r>
         </is>
       </c>
@@ -4462,16 +4629,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭 저축계좌 내 자녀 저축액·부모 부담금이 조금씩 쌓임</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-저축액을 확인하며 성취감 느낌</t>
+            <t>부모 수락 확인 후 매칭저축 시작</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+꾸준히 모으는 루틴 형성</t>
           </r>
         </is>
       </c>
@@ -4489,7 +4656,7 @@
       </c>
       <c r="B87" s="18" t="inlineStr">
         <is>
-          <t>⭐ 핵심</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C87" s="19" t="inlineStr">
@@ -4501,30 +4668,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭 저축 목표 달성</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-"내가 설계한 목표 달성" 주체감 경험</t>
-          </r>
-        </is>
-      </c>
-      <c r="D87" s="20" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="009C2B2B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>E-4</t>
-          </r>
+            <t>매칭 저축계좌 내 자녀 저축액·부모 부담금이 조금씩 쌓임</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+저축액을 확인하며 성취감 느낌</t>
+          </r>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4695,7 @@
       </c>
       <c r="B88" s="18" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>⭐ 핵심</t>
         </is>
       </c>
       <c r="C88" s="19" t="inlineStr">
@@ -4548,16 +4707,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>월간 리포트 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀의 자율 제안·투자 운용 패턴이 안정되었음을 인식</t>
+            <t>매칭 저축 목표 달성</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+"내가 설계한 목표 달성" 주체감 경험</t>
           </r>
         </is>
       </c>
@@ -4567,10 +4726,27 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
+              <color rgb="009C2B2B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>E-4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
               <color rgb="003F4F8B"/>
               <sz val="11"/>
             </rPr>
-            <t>F-1</t>
+            <t>F-9</t>
           </r>
         </is>
       </c>
@@ -4583,7 +4759,7 @@
       </c>
       <c r="B89" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C89" s="19" t="inlineStr">
@@ -4595,22 +4771,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>이벤트 자금 투자계좌로 지속해서 저축</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-세뱃돈·조부모 용돈 입금</t>
-          </r>
-        </is>
-      </c>
-      <c r="D89" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>월간 리포트 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀의 자율 제안·투자 운용 패턴이 안정되었음을 인식</t>
+          </r>
+        </is>
+      </c>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-1</t>
+          </r>
         </is>
       </c>
     </row>
@@ -4634,30 +4818,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>사고 싶은 투자상품 선택 후 제안</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-이유와 금액 정리해 부모에게 제안 발송. 구매하고 싶은 종목에 대해 부모를 설득</t>
-          </r>
-        </is>
-      </c>
-      <c r="D90" s="20" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-5</t>
-          </r>
+            <t>이벤트 자금 투자계좌로 지속해서 저축</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+세뱃돈·조부모 용돈 입금</t>
+          </r>
+        </is>
+      </c>
+      <c r="D90" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4845,7 @@
       </c>
       <c r="B91" s="18" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C91" s="19" t="inlineStr">
@@ -4681,16 +4857,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>자녀 선택 확인 후 매수 실행</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-부모) 수익보다 과정에 집중하게 해달라는 피드백 또는 수락</t>
+            <t>사고 싶은 투자상품 선택 후 제안</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+이유와 금액 정리해 부모에게 제안 발송. 구매하고 싶은 종목에 대해 부모를 설득</t>
           </r>
         </is>
       </c>
@@ -4703,7 +4879,7 @@
               <color rgb="00C65911"/>
               <sz val="11"/>
             </rPr>
-            <t>D-8</t>
+            <t>D-5</t>
           </r>
         </is>
       </c>
@@ -4716,7 +4892,7 @@
       </c>
       <c r="B92" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C92" s="19" t="inlineStr">
@@ -4728,16 +4904,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매수 후 수익률 상승 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-"내가 고른 게 올랐어!" 안내 메시지 제공</t>
+            <t>자녀 선택 확인 후 매수 실행</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+부모) 수익보다 과정에 집중하게 해달라는 피드백 또는 수락</t>
           </r>
         </is>
       </c>
@@ -4747,10 +4923,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="11"/>
-            </rPr>
-            <t>A-8</t>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-8</t>
           </r>
         </is>
       </c>
@@ -4763,7 +4939,7 @@
       </c>
       <c r="B93" s="18" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C93" s="19" t="inlineStr">
@@ -4775,22 +4951,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>첫 투자상품 매수 완료 넛지 → 부모</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀의 첫 매수 시점 알림</t>
-          </r>
-        </is>
-      </c>
-      <c r="D93" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>매수 후 수익률 상승 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+"내가 고른 게 올랐어!" 안내 메시지 제공</t>
+          </r>
+        </is>
+      </c>
+      <c r="D93" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-8</t>
+          </r>
         </is>
       </c>
     </row>
@@ -4802,7 +4986,7 @@
       </c>
       <c r="B94" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C94" s="19" t="inlineStr">
@@ -4814,30 +4998,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>투자 후 마이너스 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-"내 돈이 줄었어" 당황. 팔고 싶은 충동 발생</t>
-          </r>
-        </is>
-      </c>
-      <c r="D94" s="20" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="11"/>
-            </rPr>
-            <t>A-9</t>
-          </r>
+            <t>첫 투자상품 매수 완료 넛지 → 부모</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀의 첫 매수 시점 알림</t>
+          </r>
+        </is>
+      </c>
+      <c r="D94" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4849,7 +5025,7 @@
       </c>
       <c r="B95" s="18" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C95" s="19" t="inlineStr">
@@ -4861,16 +5037,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>수익률 마이너스 전환 넛지 → 부모</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-부모) 손실이 났을 때 부모가 자녀에게 가르쳐줘야 할 내용을 가이드 형태로 제공</t>
+            <t>투자 후 마이너스 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+"내 돈이 줄었어" 당황. 팔고 싶은 충동 발생</t>
           </r>
         </is>
       </c>
@@ -4896,7 +5072,7 @@
       </c>
       <c r="B96" s="18" t="inlineStr">
         <is>
-          <t>🔵 ⭐ 자녀</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C96" s="19" t="inlineStr">
@@ -4908,16 +5084,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>"어? 다시 올라갔어" 회복 체득</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-시간의 가치 감각으로 이해</t>
+            <t>수익률 마이너스 전환 넛지 → 부모</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+부모) 손실이 났을 때 부모가 자녀에게 가르쳐줘야 할 내용을 가이드 형태로 제공</t>
           </r>
         </is>
       </c>
@@ -4943,7 +5119,7 @@
       </c>
       <c r="B97" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🔵 ⭐ 자녀</t>
         </is>
       </c>
       <c r="C97" s="19" t="inlineStr">
@@ -4955,16 +5131,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>손실 경험 이후 "한 곳에 집중 투자하면 위험하다" 원리 인식</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-분산투자 개념 자연 학습</t>
+            <t>"어? 다시 올라갔어" 회복 체득</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+시간의 가치 감각으로 이해</t>
           </r>
         </is>
       </c>
@@ -4974,10 +5150,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00548235"/>
-              <sz val="11"/>
-            </rPr>
-            <t>C-5</t>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-9</t>
           </r>
         </is>
       </c>
@@ -5002,22 +5178,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>여러 자산에 나눠 투자하는 포트폴리오 재구성 계획 수립</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-투자 계획 및 제안</t>
-          </r>
-        </is>
-      </c>
-      <c r="D98" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>손실 경험 이후 "한 곳에 집중 투자하면 위험하다" 원리 인식</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+분산투자 개념 자연 학습</t>
+          </r>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00548235"/>
+              <sz val="11"/>
+            </rPr>
+            <t>C-5</t>
+          </r>
         </is>
       </c>
     </row>
@@ -5029,7 +5213,7 @@
       </c>
       <c r="B99" s="18" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C99" s="19" t="inlineStr">
@@ -5041,30 +5225,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>자녀 포트폴리오 구성 계획안 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-피드백 또는 수락</t>
-          </r>
-        </is>
-      </c>
-      <c r="D99" s="20" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-8</t>
-          </r>
+            <t>여러 자산에 나눠 투자하는 포트폴리오 재구성 계획 수립</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+투자 계획 및 제안</t>
+          </r>
+        </is>
+      </c>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5252,7 @@
       </c>
       <c r="B100" s="18" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C100" s="19" t="inlineStr">
@@ -5088,22 +5264,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매도 직후 회고 작성 유도 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-회고를 통해 이번 거래가 어땠는지 작성</t>
-          </r>
-        </is>
-      </c>
-      <c r="D100" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>자녀 포트폴리오 구성 계획안 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+피드백 또는 수락</t>
+          </r>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-8</t>
+          </r>
         </is>
       </c>
     </row>
@@ -5127,16 +5311,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>계좌개설 및 체크카드 발급 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-*자녀 연령 14세 도달시</t>
+            <t>매도 직후 회고 작성 유도 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+회고를 통해 이번 거래가 어땠는지 작성</t>
           </r>
         </is>
       </c>
@@ -5154,7 +5338,7 @@
       </c>
       <c r="B102" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C102" s="19" t="inlineStr">
@@ -5166,16 +5350,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>부모에게 계좌 개설 및 체크카드 발급 요청</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-본인이 먼저 주체적으로 요청하는 형태</t>
+            <t>계좌개설 및 체크카드 발급 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+*자녀 연령 14세 도달시</t>
           </r>
         </is>
       </c>
@@ -5205,16 +5389,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>월말 소비 리뷰 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-충동소비/계획소비 비율, 항목별 지출 내역 비교</t>
+            <t>부모에게 계좌 개설 및 체크카드 발급 요청</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+본인이 먼저 주체적으로 요청하는 형태</t>
           </r>
         </is>
       </c>
@@ -5244,16 +5428,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>다음 달 소비 계획 수정</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비 결정에 대한 책임감 형성</t>
+            <t>월말 소비 리뷰 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+충동소비/계획소비 비율, 항목별 지출 내역 비교</t>
           </r>
         </is>
       </c>
@@ -5283,30 +5467,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>협상 제안서 작성</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-또래 평균 대비 내 용돈 위치를 앱에서 참고해 제안서 작성</t>
-          </r>
-        </is>
-      </c>
-      <c r="D105" s="20" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-2</t>
-          </r>
+            <t>다음 달 소비 계획 수정</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비 결정에 대한 책임감 형성</t>
+          </r>
+        </is>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5494,7 @@
       </c>
       <c r="B106" s="18" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C106" s="19" t="inlineStr">
@@ -5330,16 +5506,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 인상 요청 수신</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비 내역, 또래 비교 데이터 등 확인 후 수락/거절/역제안</t>
+            <t>협상 제안서 작성</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+또래 평균 대비 내 용돈 위치를 앱에서 참고해 제안서 작성</t>
           </r>
         </is>
       </c>
@@ -5349,10 +5525,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00548235"/>
-              <sz val="11"/>
-            </rPr>
-            <t>C-1</t>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-2</t>
           </r>
         </is>
       </c>
@@ -5365,7 +5541,7 @@
       </c>
       <c r="B107" s="18" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C107" s="19" t="inlineStr">
@@ -5377,16 +5553,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>합의 내용 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-새 용돈 기준으로 자금 분할 비율 재설정</t>
+            <t>용돈 인상 요청 수신</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비 내역, 또래 비교 데이터 등 확인 후 수락/거절/역제안</t>
           </r>
         </is>
       </c>
@@ -5396,10 +5572,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-2</t>
+              <color rgb="00548235"/>
+              <sz val="11"/>
+            </rPr>
+            <t>C-1</t>
           </r>
         </is>
       </c>
@@ -5412,10 +5588,57 @@
       </c>
       <c r="B108" s="18" t="inlineStr">
         <is>
+          <t>🔵 자녀</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="10"/>
+            </rPr>
+            <t>합의 내용 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+새 용돈 기준으로 자금 분할 비율 재설정</t>
+          </r>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-2</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="50" customHeight="1">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>S3  자율 확장기 (13~15세)</t>
+        </is>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
           <t>📣 넛지</t>
         </is>
       </c>
-      <c r="C108" s="19" t="inlineStr">
+      <c r="C109" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5437,7 +5660,7 @@
           </r>
         </is>
       </c>
-      <c r="D108" s="20" t="inlineStr">
+      <c r="D109" s="20" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5448,45 +5671,6 @@
             </rPr>
             <t>D-7</t>
           </r>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="50" customHeight="1">
-      <c r="A109" s="22" t="inlineStr">
-        <is>
-          <t>S4  독립 준비기 (16~18세)</t>
-        </is>
-      </c>
-      <c r="B109" s="23" t="inlineStr">
-        <is>
-          <t>이벤트</t>
-        </is>
-      </c>
-      <c r="C109" s="24" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="10"/>
-            </rPr>
-            <t>자녀 고등학교 입학</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비 패턴 성찰 단계 진입</t>
-          </r>
-        </is>
-      </c>
-      <c r="D109" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5682,7 @@
       </c>
       <c r="B110" s="23" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>이벤트</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
@@ -5510,16 +5694,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 주기 변경 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀) 분기로 용돈을 받아 더 큰 금액을 자유롭게 계획해서 소비</t>
+            <t>자녀 고등학교 입학</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비 패턴 성찰 단계 진입</t>
           </r>
         </is>
       </c>
@@ -5549,16 +5733,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>장기 소비 계획 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀) 큰 지출이 있는지 확인하며 미리 잡아두라는 안내</t>
+            <t>용돈 주기 변경 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀) 분기로 용돈을 받아 더 큰 금액을 자유롭게 계획해서 소비</t>
           </r>
         </is>
       </c>
@@ -5588,30 +5772,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>월말 소비 리뷰 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-이 달 목표 대비 어느 정도 소비했는지에 대한 안내</t>
-          </r>
-        </is>
-      </c>
-      <c r="D112" s="26" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-1</t>
-          </r>
+            <t>장기 소비 계획 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀) 큰 지출이 있는지 확인하며 미리 잡아두라는 안내</t>
+          </r>
+        </is>
+      </c>
+      <c r="D112" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5799,7 @@
       </c>
       <c r="B113" s="23" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
@@ -5635,16 +5811,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>S4 전환 결정</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자율 운용 및 범위 허락 구조로 "이제 막을 것만 정하고 나머지는 맡겨도 되겠다"</t>
+            <t>월말 소비 리뷰 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+이 달 목표 대비 어느 정도 소비했는지에 대한 안내</t>
           </r>
         </is>
       </c>
@@ -5654,10 +5830,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-6</t>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-1</t>
           </r>
         </is>
       </c>
@@ -5682,16 +5858,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>자녀에게 차단할 고위험 상품군 선택</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-(파생상품·레버리지 ETF 등)</t>
+            <t>S4 전환 결정</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자율 운용 및 범위 허락 구조로 "이제 막을 것만 정하고 나머지는 맡겨도 되겠다"</t>
           </r>
         </is>
       </c>
@@ -5701,10 +5877,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="003F4F8B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>F-4</t>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-6</t>
           </r>
         </is>
       </c>
@@ -5717,7 +5893,7 @@
       </c>
       <c r="B115" s="23" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C115" s="24" t="inlineStr">
@@ -5729,22 +5905,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>"범위 안에서는 부모님 허락 없이 바로 실행된다"</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자유와 책임 동시 인식</t>
-          </r>
-        </is>
-      </c>
-      <c r="D115" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>자녀에게 차단할 고위험 상품군 선택</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+(파생상품·레버리지 ETF 등)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D115" s="26" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-12</t>
+          </r>
         </is>
       </c>
     </row>
@@ -5768,16 +5952,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 주기 변경 요청</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-분기 단위로 더 큰 금액 받기 요청</t>
+            <t>"범위 안에서는 부모님 허락 없이 바로 실행된다"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자유와 책임 동시 인식</t>
           </r>
         </is>
       </c>
@@ -5795,7 +5979,7 @@
       </c>
       <c r="B117" s="23" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C117" s="24" t="inlineStr">
@@ -5807,30 +5991,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 월→분기 전환</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-분기 수령 안내</t>
-          </r>
-        </is>
-      </c>
-      <c r="D117" s="26" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-3</t>
-          </r>
+            <t>용돈 주기 변경 요청</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+분기 단위로 더 큰 금액 받기 요청</t>
+          </r>
+        </is>
+      </c>
+      <c r="D117" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5842,7 +6018,7 @@
       </c>
       <c r="B118" s="23" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C118" s="24" t="inlineStr">
@@ -5854,16 +6030,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>분기 수령 용돈을 소비·저축·투자로 스스로 배분</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비 현황 확인 후 결정</t>
+            <t>용돈 월→분기 전환</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+분기 수령 안내</t>
           </r>
         </is>
       </c>
@@ -5873,10 +6049,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="00B89B0E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>B-2</t>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-3</t>
           </r>
         </is>
       </c>
@@ -5901,22 +6077,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>여행/학원 등 큰 지출 목표를 앱에 설정</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-투자 수익으로 충당할 것, 용돈에서 아낄 것 구분</t>
-          </r>
-        </is>
-      </c>
-      <c r="D119" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>분기 수령 용돈을 소비·저축·투자로 스스로 배분</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비 현황 확인 후 결정</t>
+          </r>
+        </is>
+      </c>
+      <c r="D119" s="26" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00B89B0E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>B-2</t>
+          </r>
         </is>
       </c>
     </row>
@@ -5940,30 +6124,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>체크카드로 일상 소비 자율 관리</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-월 한도 내에서 스스로 조절</t>
-          </r>
-        </is>
-      </c>
-      <c r="D120" s="26" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="003F4F8B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>F-4</t>
-          </r>
+            <t>여행/학원 등 큰 지출 목표를 앱에 설정</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+투자 수익으로 충당할 것, 용돈에서 아낄 것 구분</t>
+          </r>
+        </is>
+      </c>
+      <c r="D120" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5975,7 +6151,7 @@
       </c>
       <c r="B121" s="23" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C121" s="24" t="inlineStr">
@@ -5987,22 +6163,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>분기·학기 리포트로 큰 흐름만 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-큰 흐름만 점검</t>
-          </r>
-        </is>
-      </c>
-      <c r="D121" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>체크카드로 일상 소비 자율 관리</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+월 한도 내에서 스스로 조절</t>
+          </r>
+        </is>
+      </c>
+      <c r="D121" s="26" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-12</t>
+          </r>
         </is>
       </c>
     </row>
@@ -6014,7 +6198,7 @@
       </c>
       <c r="B122" s="23" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C122" s="24" t="inlineStr">
@@ -6026,22 +6210,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>매칭 저축 목표 스스로 설정·자동 운영</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-(부모 개별 승인 없이, 정해진 비율 내에서)</t>
-          </r>
-        </is>
-      </c>
-      <c r="D122" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>분기·학기 리포트로 큰 흐름만 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+큰 흐름만 점검</t>
+          </r>
+        </is>
+      </c>
+      <c r="D122" s="26" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-3</t>
+          </r>
         </is>
       </c>
     </row>
@@ -6053,7 +6245,7 @@
       </c>
       <c r="B123" s="23" t="inlineStr">
         <is>
-          <t>이벤트</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C123" s="24" t="inlineStr">
@@ -6065,16 +6257,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>첫 아르바이트</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-노동소득 직접 경험. "내가 번 돈을 투자한다" 자립감</t>
+            <t>매칭 저축 목표 스스로 설정·자동 운영</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+(부모 개별 승인 없이, 정해진 비율 내에서)</t>
           </r>
         </is>
       </c>
@@ -6092,7 +6284,7 @@
       </c>
       <c r="B124" s="23" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>이벤트</t>
         </is>
       </c>
       <c r="C124" s="24" t="inlineStr">
@@ -6104,30 +6296,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>알바비 들어오자마자 "얼마를 주식에 넣지?" 고민</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-이미 습관화된 사고</t>
-          </r>
-        </is>
-      </c>
-      <c r="D124" s="26" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="11"/>
-            </rPr>
-            <t>A-11</t>
-          </r>
+            <t>첫 아르바이트</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+노동소득 직접 경험. "내가 번 돈을 투자한다" 자립감</t>
+          </r>
+        </is>
+      </c>
+      <c r="D124" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6323,7 @@
       </c>
       <c r="B125" s="23" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C125" s="24" t="inlineStr">
@@ -6151,16 +6335,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>알바 소득 입금 감지 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-수입이 늘었다는 것을 자동으로 감지</t>
+            <t>알바비 들어오자마자 "얼마를 주식에 넣지?" 고민</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+이미 습관화된 사고</t>
           </r>
         </is>
       </c>
@@ -6170,10 +6354,10 @@
             <rPr>
               <rFont val="맑은 고딕"/>
               <b val="1"/>
-              <color rgb="003F4F8B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>F-2</t>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-11</t>
           </r>
         </is>
       </c>
@@ -6186,7 +6370,7 @@
       </c>
       <c r="B126" s="23" t="inlineStr">
         <is>
-          <t>🔵 ⭐ 자녀</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C126" s="24" t="inlineStr">
@@ -6198,22 +6382,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 + 알바비를 합산해 "총 수입" 개념으로 처음 관리</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-수입/지출 프레임으로 사고 전환</t>
-          </r>
-        </is>
-      </c>
-      <c r="D126" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>알바 소득 입금 감지 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+수입이 늘었다는 것을 자동으로 감지</t>
+          </r>
+        </is>
+      </c>
+      <c r="D126" s="26" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-6</t>
+          </r>
         </is>
       </c>
     </row>
@@ -6225,7 +6417,7 @@
       </c>
       <c r="B127" s="23" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🔵 ⭐ 자녀</t>
         </is>
       </c>
       <c r="C127" s="24" t="inlineStr">
@@ -6237,16 +6429,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>알바비 배분</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비/저축/투자 비율을 스스로 결정</t>
+            <t>용돈 + 알바비를 합산해 "총 수입" 개념으로 처음 관리</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+수입/지출 프레임으로 사고 전환</t>
           </r>
         </is>
       </c>
@@ -6276,16 +6468,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>허락 범위 안에서 투자 종목 매수</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-부모 개입 없이 자녀 스스로 결정</t>
+            <t>알바비 배분</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비/저축/투자 비율을 스스로 결정</t>
           </r>
         </is>
       </c>
@@ -6315,16 +6507,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>ETF 소액 정기 매수 시작</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-아르바이트 월급날 정기 매수로 습관화</t>
+            <t>허락 범위 안에서 투자 종목 매수</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+부모 개입 없이 자녀 스스로 결정</t>
           </r>
         </is>
       </c>
@@ -6354,30 +6546,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>스스로 매도 결정</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-손절 또는 익절을 부모 동의 없이 직접 실행</t>
-          </r>
-        </is>
-      </c>
-      <c r="D130" s="26" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00C65911"/>
-              <sz val="11"/>
-            </rPr>
-            <t>D-1</t>
-          </r>
+            <t>ETF 소액 정기 매수 시작</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+아르바이트 월급날 정기 매수로 습관화</t>
+          </r>
+        </is>
+      </c>
+      <c r="D130" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6573,7 @@
       </c>
       <c r="B131" s="23" t="inlineStr">
         <is>
-          <t>⭐ 핵심</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C131" s="24" t="inlineStr">
@@ -6401,22 +6585,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>책임감 내재화</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-수익이든 손실이든 내가 결정한 결과로 받아들임</t>
-          </r>
-        </is>
-      </c>
-      <c r="D131" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>스스로 매도 결정</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+손절 또는 익절을 부모 동의 없이 직접 실행</t>
+          </r>
+        </is>
+      </c>
+      <c r="D131" s="26" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00C65911"/>
+              <sz val="11"/>
+            </rPr>
+            <t>D-1</t>
+          </r>
         </is>
       </c>
     </row>
@@ -6428,7 +6620,7 @@
       </c>
       <c r="B132" s="23" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>⭐ 핵심</t>
         </is>
       </c>
       <c r="C132" s="24" t="inlineStr">
@@ -6440,30 +6632,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>종목별 비중 수정 필요 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-목표 비율 대비 특정 투자상품의 비중이 높아졌을 경우</t>
-          </r>
-        </is>
-      </c>
-      <c r="D132" s="26" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00548235"/>
-              <sz val="11"/>
-            </rPr>
-            <t>C-4</t>
-          </r>
+            <t>책임감 내재화</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+수익이든 손실이든 내가 결정한 결과로 받아들임</t>
+          </r>
+        </is>
+      </c>
+      <c r="D132" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6659,7 @@
       </c>
       <c r="B133" s="23" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C133" s="24" t="inlineStr">
@@ -6487,16 +6671,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>자산 현황 점검</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-종목별 비중이 목표 비율과 얼마나 달라졌는지 확인</t>
+            <t>종목별 비중 수정 필요 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+목표 비율 대비 특정 투자상품의 비중이 높아졌을 경우</t>
           </r>
         </is>
       </c>
@@ -6522,10 +6706,57 @@
       </c>
       <c r="B134" s="23" t="inlineStr">
         <is>
+          <t>🔵 자녀</t>
+        </is>
+      </c>
+      <c r="C134" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="10"/>
+            </rPr>
+            <t>자산 현황 점검</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+종목별 비중이 목표 비율과 얼마나 달라졌는지 확인</t>
+          </r>
+        </is>
+      </c>
+      <c r="D134" s="26" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00548235"/>
+              <sz val="11"/>
+            </rPr>
+            <t>C-4</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="50" customHeight="1">
+      <c r="A135" s="22" t="inlineStr">
+        <is>
+          <t>S4  독립 준비기 (16~18세)</t>
+        </is>
+      </c>
+      <c r="B135" s="23" t="inlineStr">
+        <is>
           <t>⭐ 핵심</t>
         </is>
       </c>
-      <c r="C134" s="24" t="inlineStr">
+      <c r="C135" s="24" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6547,56 +6778,9 @@
           </r>
         </is>
       </c>
-      <c r="D134" s="25" t="inlineStr">
+      <c r="D135" s="25" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="50" customHeight="1">
-      <c r="A135" s="27" t="inlineStr">
-        <is>
-          <t>S5  독립 견습기 (19세+)</t>
-        </is>
-      </c>
-      <c r="B135" s="28" t="inlineStr">
-        <is>
-          <t>이벤트</t>
-        </is>
-      </c>
-      <c r="C135" s="29" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="001F3864"/>
-              <sz val="10"/>
-            </rPr>
-            <t>자녀 성년 도달</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-주민등록증 발급 / 대학 진학</t>
-          </r>
-        </is>
-      </c>
-      <c r="D135" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="003F4F8B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>F-7</t>
-          </r>
         </is>
       </c>
     </row>
@@ -6608,7 +6792,7 @@
       </c>
       <c r="B136" s="28" t="inlineStr">
         <is>
-          <t>⭐ 핵심</t>
+          <t>이벤트</t>
         </is>
       </c>
       <c r="C136" s="29" t="inlineStr">
@@ -6620,22 +6804,47 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>성년 도달 (시스템)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-법적 대리 해소 · 완전 독립 안내</t>
-          </r>
-        </is>
-      </c>
-      <c r="D136" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>자녀 성년 도달</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+주민등록증 발급 / 대학 진학</t>
+          </r>
+        </is>
+      </c>
+      <c r="D136" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-10</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-15</t>
+          </r>
         </is>
       </c>
     </row>
@@ -6647,7 +6856,7 @@
       </c>
       <c r="B137" s="28" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>⭐ 핵심</t>
         </is>
       </c>
       <c r="C137" s="29" t="inlineStr">
@@ -6659,47 +6868,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>리포트·재무제표 등 모든 모니터링 권한 자동 해제</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-누적 자산 연대기 총정리</t>
-          </r>
-        </is>
-      </c>
-      <c r="D137" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="11"/>
-            </rPr>
-            <t>A-7</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ·  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="003F4F8B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>F-7</t>
-          </r>
+            <t>성년 도달 (시스템)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+법적 대리 해소 · 완전 독립 안내</t>
+          </r>
+        </is>
+      </c>
+      <c r="D137" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6895,7 @@
       </c>
       <c r="B138" s="28" t="inlineStr">
         <is>
-          <t>📣 넛지</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C138" s="29" t="inlineStr">
@@ -6723,16 +6907,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>증여 관련 안내 → 부모</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-공제 한도 변경 안내 (5,000만원). 자산 변화 시각화. 분할 증여 안내. 성인 자녀 증여 관리 및 실행</t>
+            <t>리포트·재무제표 등 모든 모니터링 권한 자동 해제</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+누적 자산 연대기 총정리</t>
           </r>
         </is>
       </c>
@@ -6745,7 +6929,7 @@
               <color rgb="002F5496"/>
               <sz val="11"/>
             </rPr>
-            <t>A-13</t>
+            <t>A-7</t>
           </r>
           <r>
             <rPr>
@@ -6762,7 +6946,7 @@
               <color rgb="003F4F8B"/>
               <sz val="11"/>
             </rPr>
-            <t>F-6</t>
+            <t>F-2</t>
           </r>
           <r>
             <rPr>
@@ -6779,24 +6963,7 @@
               <color rgb="003F4F8B"/>
               <sz val="11"/>
             </rPr>
-            <t>F-8</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ·  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="003F4F8B"/>
-              <sz val="11"/>
-            </rPr>
-            <t>F-9</t>
+            <t>F-15</t>
           </r>
         </is>
       </c>
@@ -6821,22 +6988,81 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 주기 변경 넛지 → 자녀</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자녀) 1년 기준 용돈을 받아 더 큰 금액 운용</t>
-          </r>
-        </is>
-      </c>
-      <c r="D139" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>증여 관련 안내 → 부모</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+공제 한도 변경 안내 (5,000만원). 자산 변화 시각화. 분할 증여 안내. 성인 자녀 증여 관리 및 실행</t>
+          </r>
+        </is>
+      </c>
+      <c r="D139" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-13</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-4</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-14</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ·  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="003F4F8B"/>
+              <sz val="11"/>
+            </rPr>
+            <t>F-16</t>
+          </r>
         </is>
       </c>
     </row>
@@ -6848,7 +7074,7 @@
       </c>
       <c r="B140" s="28" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>📣 넛지</t>
         </is>
       </c>
       <c r="C140" s="29" t="inlineStr">
@@ -6860,16 +7086,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>부모 모니터링 사라짐</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-완전한 프라이버시 생김</t>
+            <t>용돈 주기 변경 넛지 → 자녀</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자녀) 1년 기준 용돈을 받아 더 큰 금액 운용</t>
           </r>
         </is>
       </c>
@@ -6899,16 +7125,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>용돈 주기 및 금액 변경 요청</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-진정한 독립 / 용돈 금액 변경</t>
+            <t>부모 모니터링 사라짐</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+완전한 프라이버시 생김</t>
           </r>
         </is>
       </c>
@@ -6926,7 +7152,7 @@
       </c>
       <c r="B142" s="28" t="inlineStr">
         <is>
-          <t>🟢 부모</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C142" s="29" t="inlineStr">
@@ -6938,16 +7164,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>정기 생활비·용돈 송금</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-연도별 용돈 송금</t>
+            <t>용돈 주기 및 금액 변경 요청</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+진정한 독립 / 용돈 금액 변경</t>
           </r>
         </is>
       </c>
@@ -6965,7 +7191,7 @@
       </c>
       <c r="B143" s="28" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>🟢 부모</t>
         </is>
       </c>
       <c r="C143" s="29" t="inlineStr">
@@ -6977,16 +7203,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>생활비·용돈 등 아이부자로 수령 및 관리</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-소비·저축·투자로 스스로 배분</t>
+            <t>정기 생활비·용돈 송금</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+연도별 용돈 송금</t>
           </r>
         </is>
       </c>
@@ -7016,16 +7242,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>단기-중기-장기 목표에 따른 자산 관리/증식 계획 수립</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-자산 증식 전략 수립</t>
+            <t>생활비·용돈 등 아이부자로 수령 및 관리</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+소비·저축·투자로 스스로 배분</t>
           </r>
         </is>
       </c>
@@ -7055,16 +7281,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>다음 투자 전략 스스로 정비</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-S0부터 현재까지 내가 한 결정들 및 기록들을 돌아봄</t>
+            <t>단기-중기-장기 목표에 따른 자산 관리/증식 계획 수립</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+자산 증식 전략 수립</t>
           </r>
         </is>
       </c>
@@ -7082,7 +7308,7 @@
       </c>
       <c r="B146" s="28" t="inlineStr">
         <is>
-          <t>⭐ 핵심</t>
+          <t>🔵 자녀</t>
         </is>
       </c>
       <c r="C146" s="29" t="inlineStr">
@@ -7094,30 +7320,22 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>투자 연대기 확인</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-S0~현재 의사결정 히스토리 회고</t>
-          </r>
-        </is>
-      </c>
-      <c r="D146" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="002F5496"/>
-              <sz val="11"/>
-            </rPr>
-            <t>A-7</t>
-          </r>
+            <t>다음 투자 전략 스스로 정비</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+S0부터 현재까지 내가 한 결정들 및 기록들을 돌아봄</t>
+          </r>
+        </is>
+      </c>
+      <c r="D146" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7347,7 @@
       </c>
       <c r="B147" s="28" t="inlineStr">
         <is>
-          <t>🔵 자녀</t>
+          <t>⭐ 핵심</t>
         </is>
       </c>
       <c r="C147" s="29" t="inlineStr">
@@ -7141,22 +7359,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>기존 투자 계좌 지속 운용</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-아르바이트, 월급 등 수익 투자</t>
-          </r>
-        </is>
-      </c>
-      <c r="D147" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>투자 연대기 확인</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+S0~현재 의사결정 히스토리 회고</t>
+          </r>
+        </is>
+      </c>
+      <c r="D147" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-7</t>
+          </r>
         </is>
       </c>
     </row>
@@ -7180,16 +7406,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>투자 금액 증가 및 포트폴리오 다양화</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-코인 등 포트폴리오 종목 다양화</t>
+            <t>기존 투자 계좌 지속 운용</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+아르바이트, 월급 등 수익 투자</t>
           </r>
         </is>
       </c>
@@ -7219,22 +7445,30 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>성인용 금융상품 가입 및 운용</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-신용카드 발급</t>
-          </r>
-        </is>
-      </c>
-      <c r="D149" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
+            <t>투자 금액 증가 및 포트폴리오 다양화</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+코인 등 포트폴리오 종목 다양화</t>
+          </r>
+        </is>
+      </c>
+      <c r="D149" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="002F5496"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A-12</t>
+          </r>
         </is>
       </c>
     </row>
@@ -7258,16 +7492,16 @@
               <color rgb="001F3864"/>
               <sz val="10"/>
             </rPr>
-            <t>절세 관련 상품 탐색 및 가입</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00404040"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">
-ISA, IRP 등 절세 관련 상품 가입</t>
+            <t>성인용 금융상품 가입 및 운용</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+신용카드 발급</t>
           </r>
         </is>
       </c>
@@ -7285,10 +7519,49 @@
       </c>
       <c r="B151" s="28" t="inlineStr">
         <is>
+          <t>🔵 자녀</t>
+        </is>
+      </c>
+      <c r="C151" s="29" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="10"/>
+            </rPr>
+            <t>절세 관련 상품 탐색 및 가입</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00404040"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+ISA, IRP 등 절세 관련 상품 가입</t>
+          </r>
+        </is>
+      </c>
+      <c r="D151" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="50" customHeight="1">
+      <c r="A152" s="27" t="inlineStr">
+        <is>
+          <t>S5  독립 견습기 (19세+)</t>
+        </is>
+      </c>
+      <c r="B152" s="28" t="inlineStr">
+        <is>
           <t>📣 넛지</t>
         </is>
       </c>
-      <c r="C151" s="29" t="inlineStr">
+      <c r="C152" s="29" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7310,7 +7583,7 @@
           </r>
         </is>
       </c>
-      <c r="D151" s="31" t="inlineStr">
+      <c r="D152" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
